--- a/customer_service_forms/002_spa_evaluation_form--customer_service_forms.xlsx
+++ b/customer_service_forms/002_spa_evaluation_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>spa_evaluation_form</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spa_evaluation_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please share your experience with our SPA service.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_information</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide your name.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medical_information</t>
+          <t>customer_since</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>medical_information</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How long have you been a customer?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide the number of months/years you've been with us.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>product_evaluation</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>product_evaluation</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Medical Condition</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please describe any medical conditions we should be aware of.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>service_availability</t>
+          <t>medical_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>service_availability</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you have any medical conditions?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please answer 'Yes' or 'No'.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>product_rating</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Product/Service Rating</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate our product/service (Good, Fair, Excellent, Bad, Very Bad)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_services</t>
+          <t>evaluation_process</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_services</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Evaluation Process</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe our evaluation process.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_condition</t>
+          <t>eval_clear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Was the evaluation process clear?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Yes or No.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,23 +731,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>customer_satisfaction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Customer Satisfaction</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate your satisfaction (Satisfied, Dissatisfied)</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,38 +763,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>evaluation_process</t>
+          <t>eval_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>evaluation_process</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Why are you satisfied/dissatisfied?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide a brief description.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>product_rating</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>product_rating</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Share anything else you'd like to tell us about your experience.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,320 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>customer_satisfaction</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>customer_satisfaction</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Suggestions</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Do you have any suggestions for improving our service?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>evaluation_process</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>evaluation_process</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>product_rating</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>product_rating</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>customer_satisfaction</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>customer_satisfaction</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>evaluation_process</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>evaluation_process</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>product_rating</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>product_rating</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_satisfaction</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>customer_satisfaction</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>medical_condition</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>evaluation_process</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>evaluation_process</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_services_choices</t>
+          <t>medical_info_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +892,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_services_choices</t>
+          <t>medical_info_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1165,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1182,12 +931,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1199,12 +948,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1245,34 +994,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_satisfaction_choices</t>
+          <t>eval_clear_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_satisfaction_choices</t>
+          <t>eval_clear_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1033,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1301,163 +1050,10 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>Somewhat Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Very Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>product_rating_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>product_rating_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>dissatisfied</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>product_rating_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>product_rating_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>dissatisfied</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Dissatisfied</t>
         </is>
